--- a/test/data/excel/XNT_app_test.xlsx
+++ b/test/data/excel/XNT_app_test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nguyendn/Desktop/cim/import-export-backend/test/data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{054FBC5A-A6B1-A14D-B74A-A737B7EBBD70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79CD0044-F69E-8F40-A17C-A3327EB0CFBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="640" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="600" yWindow="640" windowWidth="29640" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="THANG 11" sheetId="2" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="42">
   <si>
     <t>CĂN TIN ĐẠI HỌC NGÂN HÀNG</t>
   </si>
@@ -510,7 +510,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
@@ -636,18 +636,9 @@
     <xf numFmtId="169" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -665,10 +656,6 @@
     </xf>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="2" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -757,6 +744,42 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -769,49 +792,40 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="2" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="2" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="2" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -825,9 +839,9 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="FFFFFF99"/>
       <color rgb="FFDDDDDD"/>
       <color rgb="FFAAAAAA"/>
+      <color rgb="FFFFFF99"/>
       <color rgb="FFFAFAFA"/>
     </mruColors>
   </colors>
@@ -1204,7 +1218,7 @@
   <dimension ref="A2:CM34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="18" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="31.1640625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="23" style="2" customWidth="1"/>
     <col min="2" max="2" width="6.83203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="60.83203125" style="31" customWidth="1"/>
     <col min="4" max="4" width="10.83203125" style="1" customWidth="1"/>
@@ -1346,549 +1360,551 @@
       <c r="BQ4" s="28"/>
     </row>
     <row r="5" spans="1:91" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="76" t="s">
+      <c r="A5" s="71" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="79" t="s">
+      <c r="B5" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="67" t="s">
+      <c r="C5" s="62" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="70" t="s">
+      <c r="D5" s="65" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="73" t="s">
+      <c r="E5" s="68" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="98" t="s">
+      <c r="F5" s="93" t="s">
         <v>3</v>
       </c>
-      <c r="G5" s="98"/>
-      <c r="H5" s="96" t="s">
+      <c r="G5" s="93"/>
+      <c r="H5" s="86" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="96"/>
-      <c r="J5" s="96"/>
-      <c r="K5" s="96"/>
-      <c r="L5" s="96"/>
-      <c r="M5" s="96"/>
-      <c r="N5" s="96"/>
-      <c r="O5" s="96"/>
-      <c r="P5" s="96"/>
-      <c r="Q5" s="96"/>
-      <c r="R5" s="96"/>
-      <c r="S5" s="96"/>
-      <c r="T5" s="96"/>
-      <c r="U5" s="96"/>
-      <c r="V5" s="96"/>
-      <c r="W5" s="96"/>
-      <c r="X5" s="96"/>
-      <c r="Y5" s="96"/>
-      <c r="Z5" s="96"/>
-      <c r="AA5" s="96"/>
-      <c r="AB5" s="96"/>
-      <c r="AC5" s="96"/>
-      <c r="AD5" s="96"/>
-      <c r="AE5" s="96"/>
-      <c r="AF5" s="96"/>
-      <c r="AG5" s="96"/>
-      <c r="AH5" s="96"/>
-      <c r="AI5" s="96"/>
-      <c r="AJ5" s="96"/>
-      <c r="AK5" s="96"/>
-      <c r="AL5" s="96"/>
-      <c r="AM5" s="96"/>
-      <c r="AN5" s="96"/>
-      <c r="AO5" s="96"/>
-      <c r="AP5" s="96"/>
-      <c r="AQ5" s="96"/>
-      <c r="AR5" s="96"/>
-      <c r="AS5" s="96"/>
-      <c r="AT5" s="96"/>
-      <c r="AU5" s="96"/>
-      <c r="AV5" s="96"/>
-      <c r="AW5" s="96"/>
-      <c r="AX5" s="96"/>
-      <c r="AY5" s="96"/>
-      <c r="AZ5" s="96"/>
-      <c r="BA5" s="96"/>
-      <c r="BB5" s="96"/>
-      <c r="BC5" s="96"/>
-      <c r="BD5" s="96"/>
-      <c r="BE5" s="96"/>
-      <c r="BF5" s="96"/>
-      <c r="BG5" s="96"/>
-      <c r="BH5" s="96"/>
-      <c r="BI5" s="96"/>
-      <c r="BJ5" s="96"/>
-      <c r="BK5" s="96"/>
-      <c r="BL5" s="96"/>
-      <c r="BM5" s="96"/>
-      <c r="BN5" s="96"/>
-      <c r="BO5" s="96"/>
-      <c r="BP5" s="96"/>
-      <c r="BQ5" s="96"/>
-      <c r="BR5" s="90" t="s">
+      <c r="I5" s="86"/>
+      <c r="J5" s="86"/>
+      <c r="K5" s="86"/>
+      <c r="L5" s="86"/>
+      <c r="M5" s="86"/>
+      <c r="N5" s="86"/>
+      <c r="O5" s="86"/>
+      <c r="P5" s="86"/>
+      <c r="Q5" s="86"/>
+      <c r="R5" s="86"/>
+      <c r="S5" s="86"/>
+      <c r="T5" s="86"/>
+      <c r="U5" s="86"/>
+      <c r="V5" s="86"/>
+      <c r="W5" s="86"/>
+      <c r="X5" s="86"/>
+      <c r="Y5" s="86"/>
+      <c r="Z5" s="86"/>
+      <c r="AA5" s="86"/>
+      <c r="AB5" s="86"/>
+      <c r="AC5" s="86"/>
+      <c r="AD5" s="86"/>
+      <c r="AE5" s="86"/>
+      <c r="AF5" s="86"/>
+      <c r="AG5" s="86"/>
+      <c r="AH5" s="86"/>
+      <c r="AI5" s="86"/>
+      <c r="AJ5" s="86"/>
+      <c r="AK5" s="86"/>
+      <c r="AL5" s="86"/>
+      <c r="AM5" s="86"/>
+      <c r="AN5" s="86"/>
+      <c r="AO5" s="86"/>
+      <c r="AP5" s="86"/>
+      <c r="AQ5" s="86"/>
+      <c r="AR5" s="86"/>
+      <c r="AS5" s="86"/>
+      <c r="AT5" s="86"/>
+      <c r="AU5" s="86"/>
+      <c r="AV5" s="86"/>
+      <c r="AW5" s="86"/>
+      <c r="AX5" s="86"/>
+      <c r="AY5" s="86"/>
+      <c r="AZ5" s="86"/>
+      <c r="BA5" s="86"/>
+      <c r="BB5" s="86"/>
+      <c r="BC5" s="86"/>
+      <c r="BD5" s="86"/>
+      <c r="BE5" s="86"/>
+      <c r="BF5" s="86"/>
+      <c r="BG5" s="86"/>
+      <c r="BH5" s="86"/>
+      <c r="BI5" s="86"/>
+      <c r="BJ5" s="86"/>
+      <c r="BK5" s="86"/>
+      <c r="BL5" s="86"/>
+      <c r="BM5" s="86"/>
+      <c r="BN5" s="86"/>
+      <c r="BO5" s="86"/>
+      <c r="BP5" s="86"/>
+      <c r="BQ5" s="86"/>
+      <c r="BR5" s="80" t="s">
         <v>9</v>
       </c>
-      <c r="BS5" s="91"/>
-      <c r="BT5" s="94" t="s">
+      <c r="BS5" s="81"/>
+      <c r="BT5" s="84" t="s">
         <v>10</v>
       </c>
-      <c r="BU5" s="96" t="s">
+      <c r="BU5" s="86" t="s">
         <v>4</v>
       </c>
-      <c r="BV5" s="96"/>
-      <c r="BW5" s="96" t="s">
+      <c r="BV5" s="86"/>
+      <c r="BW5" s="86" t="s">
         <v>5</v>
       </c>
-      <c r="BX5" s="96"/>
-      <c r="BY5" s="86" t="s">
+      <c r="BX5" s="86"/>
+      <c r="BY5" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="BZ5" s="86"/>
-      <c r="CA5" s="86"/>
-      <c r="CB5" s="87" t="s">
+      <c r="BZ5" s="76"/>
+      <c r="CA5" s="76"/>
+      <c r="CB5" s="77" t="s">
         <v>39</v>
       </c>
-      <c r="CC5" s="88"/>
-      <c r="CD5" s="88"/>
-      <c r="CE5" s="89"/>
-      <c r="CF5" s="80" t="s">
+      <c r="CC5" s="78"/>
+      <c r="CD5" s="78"/>
+      <c r="CE5" s="79"/>
+      <c r="CF5" s="87" t="s">
         <v>38</v>
       </c>
-      <c r="CG5" s="81"/>
-      <c r="CH5" s="80" t="s">
+      <c r="CG5" s="88"/>
+      <c r="CH5" s="87" t="s">
         <v>41</v>
       </c>
-      <c r="CI5" s="81"/>
-      <c r="CJ5" s="80" t="s">
+      <c r="CI5" s="88"/>
+      <c r="CJ5" s="87" t="s">
         <v>40</v>
       </c>
-      <c r="CK5" s="81"/>
-      <c r="CL5" s="97" t="s">
+      <c r="CK5" s="88"/>
+      <c r="CL5" s="91" t="s">
         <v>7</v>
       </c>
-      <c r="CM5" s="97"/>
+      <c r="CM5" s="91"/>
     </row>
     <row r="6" spans="1:91" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="77"/>
-      <c r="B6" s="79"/>
-      <c r="C6" s="68"/>
-      <c r="D6" s="71"/>
-      <c r="E6" s="74"/>
-      <c r="F6" s="98"/>
-      <c r="G6" s="98"/>
-      <c r="H6" s="85">
+      <c r="A6" s="72"/>
+      <c r="B6" s="74"/>
+      <c r="C6" s="63"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="69"/>
+      <c r="F6" s="93"/>
+      <c r="G6" s="93"/>
+      <c r="H6" s="75">
         <v>1</v>
       </c>
-      <c r="I6" s="85"/>
-      <c r="J6" s="85">
+      <c r="I6" s="75"/>
+      <c r="J6" s="75">
         <v>2</v>
       </c>
-      <c r="K6" s="85"/>
-      <c r="L6" s="85">
+      <c r="K6" s="75"/>
+      <c r="L6" s="75">
         <v>3</v>
       </c>
-      <c r="M6" s="85"/>
-      <c r="N6" s="85">
+      <c r="M6" s="75"/>
+      <c r="N6" s="75">
         <v>4</v>
       </c>
-      <c r="O6" s="85"/>
-      <c r="P6" s="85">
+      <c r="O6" s="75"/>
+      <c r="P6" s="75">
         <v>5</v>
       </c>
-      <c r="Q6" s="85"/>
-      <c r="R6" s="85">
+      <c r="Q6" s="75"/>
+      <c r="R6" s="75">
         <v>6</v>
       </c>
-      <c r="S6" s="85"/>
-      <c r="T6" s="85">
+      <c r="S6" s="75"/>
+      <c r="T6" s="75">
         <v>7</v>
       </c>
-      <c r="U6" s="85"/>
-      <c r="V6" s="85">
+      <c r="U6" s="75"/>
+      <c r="V6" s="75">
         <v>8</v>
       </c>
-      <c r="W6" s="85"/>
-      <c r="X6" s="85">
+      <c r="W6" s="75"/>
+      <c r="X6" s="75">
         <v>9</v>
       </c>
-      <c r="Y6" s="85"/>
-      <c r="Z6" s="85">
+      <c r="Y6" s="75"/>
+      <c r="Z6" s="75">
         <v>10</v>
       </c>
-      <c r="AA6" s="85"/>
-      <c r="AB6" s="85">
-        <v>11</v>
-      </c>
-      <c r="AC6" s="85"/>
-      <c r="AD6" s="85">
+      <c r="AA6" s="75"/>
+      <c r="AB6" s="75">
+        <v>11</v>
+      </c>
+      <c r="AC6" s="75"/>
+      <c r="AD6" s="75">
         <v>12</v>
       </c>
-      <c r="AE6" s="85"/>
-      <c r="AF6" s="85">
+      <c r="AE6" s="75"/>
+      <c r="AF6" s="75">
         <v>13</v>
       </c>
-      <c r="AG6" s="85"/>
-      <c r="AH6" s="85">
+      <c r="AG6" s="75"/>
+      <c r="AH6" s="75">
         <v>14</v>
       </c>
-      <c r="AI6" s="85"/>
-      <c r="AJ6" s="85">
+      <c r="AI6" s="75"/>
+      <c r="AJ6" s="75">
         <v>15</v>
       </c>
-      <c r="AK6" s="85"/>
-      <c r="AL6" s="85">
+      <c r="AK6" s="75"/>
+      <c r="AL6" s="75">
         <v>16</v>
       </c>
-      <c r="AM6" s="85"/>
-      <c r="AN6" s="85">
+      <c r="AM6" s="75"/>
+      <c r="AN6" s="75">
         <v>17</v>
       </c>
-      <c r="AO6" s="85"/>
-      <c r="AP6" s="85">
+      <c r="AO6" s="75"/>
+      <c r="AP6" s="75">
         <v>18</v>
       </c>
-      <c r="AQ6" s="85"/>
-      <c r="AR6" s="85">
+      <c r="AQ6" s="75"/>
+      <c r="AR6" s="75">
         <v>19</v>
       </c>
-      <c r="AS6" s="85"/>
-      <c r="AT6" s="85">
+      <c r="AS6" s="75"/>
+      <c r="AT6" s="75">
         <v>20</v>
       </c>
-      <c r="AU6" s="85"/>
-      <c r="AV6" s="85">
+      <c r="AU6" s="75"/>
+      <c r="AV6" s="75">
         <v>21</v>
       </c>
-      <c r="AW6" s="85"/>
-      <c r="AX6" s="85">
+      <c r="AW6" s="75"/>
+      <c r="AX6" s="75">
         <v>22</v>
       </c>
-      <c r="AY6" s="85"/>
-      <c r="AZ6" s="85">
+      <c r="AY6" s="75"/>
+      <c r="AZ6" s="75">
         <v>23</v>
       </c>
-      <c r="BA6" s="85"/>
-      <c r="BB6" s="85">
+      <c r="BA6" s="75"/>
+      <c r="BB6" s="75">
         <v>24</v>
       </c>
-      <c r="BC6" s="85"/>
-      <c r="BD6" s="85">
+      <c r="BC6" s="75"/>
+      <c r="BD6" s="75">
         <v>25</v>
       </c>
-      <c r="BE6" s="85"/>
-      <c r="BF6" s="85">
+      <c r="BE6" s="75"/>
+      <c r="BF6" s="75">
         <v>26</v>
       </c>
-      <c r="BG6" s="85"/>
-      <c r="BH6" s="85">
+      <c r="BG6" s="75"/>
+      <c r="BH6" s="75">
         <v>27</v>
       </c>
-      <c r="BI6" s="85"/>
-      <c r="BJ6" s="85">
+      <c r="BI6" s="75"/>
+      <c r="BJ6" s="75">
         <v>28</v>
       </c>
-      <c r="BK6" s="85"/>
-      <c r="BL6" s="85">
+      <c r="BK6" s="75"/>
+      <c r="BL6" s="75">
         <v>29</v>
       </c>
-      <c r="BM6" s="85"/>
-      <c r="BN6" s="85">
+      <c r="BM6" s="75"/>
+      <c r="BN6" s="75">
         <v>30</v>
       </c>
-      <c r="BO6" s="85"/>
-      <c r="BP6" s="85">
+      <c r="BO6" s="75"/>
+      <c r="BP6" s="75">
         <v>31</v>
       </c>
-      <c r="BQ6" s="85"/>
-      <c r="BR6" s="92"/>
-      <c r="BS6" s="93"/>
-      <c r="BT6" s="95"/>
-      <c r="BU6" s="37" t="s">
-        <v>11</v>
-      </c>
-      <c r="BV6" s="38" t="s">
+      <c r="BQ6" s="75"/>
+      <c r="BR6" s="82"/>
+      <c r="BS6" s="83"/>
+      <c r="BT6" s="94"/>
+      <c r="BU6" s="95" t="s">
+        <v>11</v>
+      </c>
+      <c r="BV6" s="97" t="s">
         <v>13</v>
       </c>
-      <c r="BW6" s="39" t="s">
-        <v>11</v>
-      </c>
-      <c r="BX6" s="38" t="s">
+      <c r="BW6" s="99" t="s">
+        <v>11</v>
+      </c>
+      <c r="BX6" s="97" t="s">
         <v>13</v>
       </c>
-      <c r="BY6" s="40" t="s">
-        <v>11</v>
-      </c>
-      <c r="BZ6" s="38" t="s">
+      <c r="BY6" s="101" t="s">
+        <v>11</v>
+      </c>
+      <c r="BZ6" s="97" t="s">
         <v>12</v>
       </c>
-      <c r="CA6" s="38" t="s">
+      <c r="CA6" s="97" t="s">
         <v>13</v>
       </c>
-      <c r="CB6" s="84" t="s">
+      <c r="CB6" s="92" t="s">
         <v>14</v>
       </c>
-      <c r="CC6" s="84"/>
-      <c r="CD6" s="84" t="s">
+      <c r="CC6" s="92"/>
+      <c r="CD6" s="92" t="s">
         <v>28</v>
       </c>
-      <c r="CE6" s="84"/>
-      <c r="CF6" s="82"/>
-      <c r="CG6" s="83"/>
-      <c r="CH6" s="82"/>
-      <c r="CI6" s="83"/>
-      <c r="CJ6" s="82"/>
-      <c r="CK6" s="83"/>
-      <c r="CL6" s="97"/>
-      <c r="CM6" s="97"/>
+      <c r="CE6" s="92"/>
+      <c r="CF6" s="89"/>
+      <c r="CG6" s="90"/>
+      <c r="CH6" s="89"/>
+      <c r="CI6" s="90"/>
+      <c r="CJ6" s="89"/>
+      <c r="CK6" s="90"/>
+      <c r="CL6" s="91"/>
+      <c r="CM6" s="91"/>
     </row>
     <row r="7" spans="1:91" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="78"/>
-      <c r="B7" s="79"/>
-      <c r="C7" s="69"/>
-      <c r="D7" s="72"/>
-      <c r="E7" s="75"/>
-      <c r="F7" s="64" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" s="38" t="s">
+      <c r="A7" s="73"/>
+      <c r="B7" s="74"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="67"/>
+      <c r="E7" s="70"/>
+      <c r="F7" s="59" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="H7" s="43" t="s">
-        <v>11</v>
-      </c>
-      <c r="I7" s="38" t="s">
+      <c r="H7" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="I7" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="J7" s="43" t="s">
-        <v>11</v>
-      </c>
-      <c r="K7" s="38" t="s">
+      <c r="J7" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="K7" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="L7" s="43" t="s">
-        <v>11</v>
-      </c>
-      <c r="M7" s="38" t="s">
+      <c r="L7" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="M7" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="N7" s="43" t="s">
-        <v>11</v>
-      </c>
-      <c r="O7" s="38" t="s">
+      <c r="N7" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="O7" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="P7" s="43" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q7" s="38" t="s">
+      <c r="P7" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q7" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="R7" s="43" t="s">
-        <v>11</v>
-      </c>
-      <c r="S7" s="38" t="s">
+      <c r="R7" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="S7" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="T7" s="43" t="s">
-        <v>11</v>
-      </c>
-      <c r="U7" s="38" t="s">
+      <c r="T7" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="U7" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="V7" s="43" t="s">
-        <v>11</v>
-      </c>
-      <c r="W7" s="38" t="s">
+      <c r="V7" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="W7" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="X7" s="43" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y7" s="38" t="s">
+      <c r="X7" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="Y7" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="Z7" s="43" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA7" s="38" t="s">
+      <c r="Z7" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA7" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="AB7" s="43" t="s">
-        <v>11</v>
-      </c>
-      <c r="AC7" s="38" t="s">
+      <c r="AB7" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC7" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="AD7" s="43" t="s">
+      <c r="AD7" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="AE7" s="38" t="s">
+      <c r="AE7" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="AF7" s="44" t="s">
-        <v>11</v>
-      </c>
-      <c r="AG7" s="38" t="s">
+      <c r="AF7" s="41" t="s">
+        <v>11</v>
+      </c>
+      <c r="AG7" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="AH7" s="43" t="s">
-        <v>11</v>
-      </c>
-      <c r="AI7" s="38" t="s">
+      <c r="AH7" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="AI7" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="AJ7" s="43" t="s">
-        <v>11</v>
-      </c>
-      <c r="AK7" s="38" t="s">
+      <c r="AJ7" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="AK7" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="AL7" s="43" t="s">
-        <v>11</v>
-      </c>
-      <c r="AM7" s="38" t="s">
+      <c r="AL7" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="AM7" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="AN7" s="43" t="s">
-        <v>11</v>
-      </c>
-      <c r="AO7" s="38" t="s">
+      <c r="AN7" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="AO7" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="AP7" s="43" t="s">
-        <v>11</v>
-      </c>
-      <c r="AQ7" s="38" t="s">
+      <c r="AP7" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="AQ7" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="AR7" s="43" t="s">
-        <v>11</v>
-      </c>
-      <c r="AS7" s="38" t="s">
+      <c r="AR7" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="AS7" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="AT7" s="43" t="s">
-        <v>11</v>
-      </c>
-      <c r="AU7" s="38" t="s">
+      <c r="AT7" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="AU7" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="AV7" s="43" t="s">
-        <v>11</v>
-      </c>
-      <c r="AW7" s="38" t="s">
+      <c r="AV7" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="AW7" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="AX7" s="45" t="s">
-        <v>11</v>
-      </c>
-      <c r="AY7" s="38" t="s">
+      <c r="AX7" s="42" t="s">
+        <v>11</v>
+      </c>
+      <c r="AY7" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="AZ7" s="43" t="s">
-        <v>11</v>
-      </c>
-      <c r="BA7" s="38" t="s">
+      <c r="AZ7" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="BA7" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="BB7" s="43" t="s">
-        <v>11</v>
-      </c>
-      <c r="BC7" s="38" t="s">
+      <c r="BB7" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="BC7" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="BD7" s="42" t="s">
-        <v>11</v>
-      </c>
-      <c r="BE7" s="38" t="s">
+      <c r="BD7" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="BE7" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="BF7" s="43" t="s">
-        <v>11</v>
-      </c>
-      <c r="BG7" s="46" t="s">
+      <c r="BF7" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="BG7" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="BH7" s="43" t="s">
-        <v>11</v>
-      </c>
-      <c r="BI7" s="38" t="s">
+      <c r="BH7" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="BI7" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="BJ7" s="43" t="s">
-        <v>11</v>
-      </c>
-      <c r="BK7" s="38" t="s">
+      <c r="BJ7" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="BK7" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="BL7" s="43" t="s">
-        <v>11</v>
-      </c>
-      <c r="BM7" s="38" t="s">
+      <c r="BL7" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="BM7" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="BN7" s="43" t="s">
-        <v>11</v>
-      </c>
-      <c r="BO7" s="38" t="s">
+      <c r="BN7" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="BO7" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="BP7" s="43" t="s">
-        <v>11</v>
-      </c>
-      <c r="BQ7" s="38" t="s">
+      <c r="BP7" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="BQ7" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="BR7" s="43"/>
-      <c r="BS7" s="38" t="s">
+      <c r="BR7" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="BS7" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="BT7" s="47"/>
-      <c r="BU7" s="37"/>
-      <c r="BV7" s="38"/>
-      <c r="BW7" s="39"/>
-      <c r="BX7" s="38"/>
-      <c r="BY7" s="48"/>
-      <c r="BZ7" s="38"/>
-      <c r="CA7" s="38"/>
-      <c r="CB7" s="38" t="s">
-        <v>11</v>
-      </c>
-      <c r="CC7" s="38" t="s">
+      <c r="BT7" s="85"/>
+      <c r="BU7" s="96"/>
+      <c r="BV7" s="98"/>
+      <c r="BW7" s="100"/>
+      <c r="BX7" s="98"/>
+      <c r="BY7" s="102"/>
+      <c r="BZ7" s="98"/>
+      <c r="CA7" s="98"/>
+      <c r="CB7" s="37" t="s">
+        <v>11</v>
+      </c>
+      <c r="CC7" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="CD7" s="38" t="s">
-        <v>11</v>
-      </c>
-      <c r="CE7" s="38" t="s">
+      <c r="CD7" s="37" t="s">
+        <v>11</v>
+      </c>
+      <c r="CE7" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="CF7" s="38" t="s">
-        <v>11</v>
-      </c>
-      <c r="CG7" s="38" t="s">
+      <c r="CF7" s="37" t="s">
+        <v>11</v>
+      </c>
+      <c r="CG7" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="CH7" s="49" t="s">
-        <v>11</v>
-      </c>
-      <c r="CI7" s="49" t="s">
+      <c r="CH7" s="44" t="s">
+        <v>11</v>
+      </c>
+      <c r="CI7" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="CJ7" s="38" t="s">
-        <v>11</v>
-      </c>
-      <c r="CK7" s="38" t="s">
+      <c r="CJ7" s="37" t="s">
+        <v>11</v>
+      </c>
+      <c r="CK7" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="CL7" s="65" t="s">
-        <v>11</v>
-      </c>
-      <c r="CM7" s="41" t="s">
+      <c r="CL7" s="60" t="s">
+        <v>11</v>
+      </c>
+      <c r="CM7" s="38" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1908,12 +1924,10 @@
       <c r="E8" s="5">
         <v>10000</v>
       </c>
-      <c r="F8" s="6">
-        <v>10</v>
-      </c>
+      <c r="F8" s="6"/>
       <c r="G8" s="7">
         <f>F8*$E8</f>
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="H8" s="19"/>
       <c r="I8" s="17">
@@ -2092,7 +2106,7 @@
         <f>BW8*$E8</f>
         <v>0</v>
       </c>
-      <c r="BY8" s="63">
+      <c r="BY8" s="58">
         <f>BW8</f>
         <v>0</v>
       </c>
@@ -2126,7 +2140,7 @@
         <f t="shared" ref="CK8" si="33">CJ8*$E8</f>
         <v>0</v>
       </c>
-      <c r="CL8" s="66"/>
+      <c r="CL8" s="61"/>
       <c r="CM8" s="12">
         <f>CL8*$E8</f>
         <v>0</v>
@@ -2328,7 +2342,7 @@
         <f t="shared" ref="BX9:BX15" si="39">BW9*$E9</f>
         <v>0</v>
       </c>
-      <c r="BY9" s="63">
+      <c r="BY9" s="58">
         <f>BW9</f>
         <v>0</v>
       </c>
@@ -2362,7 +2376,7 @@
         <f t="shared" ref="CK9" si="43">CJ9*$E9</f>
         <v>0</v>
       </c>
-      <c r="CL9" s="66"/>
+      <c r="CL9" s="61"/>
       <c r="CM9" s="12">
         <f t="shared" ref="CM9:CM15" si="44">CL9*$E9</f>
         <v>0</v>
@@ -2566,7 +2580,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="BY10" s="63">
+      <c r="BY10" s="58">
         <f t="shared" ref="BY10:BY15" si="47">BW10</f>
         <v>0</v>
       </c>
@@ -2600,7 +2614,7 @@
         <f t="shared" ref="CK10" si="51">CJ10*$E10</f>
         <v>0</v>
       </c>
-      <c r="CL10" s="66">
+      <c r="CL10" s="61">
         <v>125</v>
       </c>
       <c r="CM10" s="12">
@@ -2804,7 +2818,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="BY11" s="63">
+      <c r="BY11" s="58">
         <f t="shared" si="47"/>
         <v>0</v>
       </c>
@@ -2838,7 +2852,7 @@
         <f t="shared" ref="CK11" si="55">CJ11*$E11</f>
         <v>0</v>
       </c>
-      <c r="CL11" s="66"/>
+      <c r="CL11" s="61"/>
       <c r="CM11" s="12">
         <f t="shared" si="44"/>
         <v>0</v>
@@ -3042,7 +3056,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="BY12" s="63">
+      <c r="BY12" s="58">
         <f t="shared" si="47"/>
         <v>0</v>
       </c>
@@ -3076,7 +3090,7 @@
         <f t="shared" ref="CK12" si="59">CJ12*$E12</f>
         <v>0</v>
       </c>
-      <c r="CL12" s="66">
+      <c r="CL12" s="61">
         <v>72</v>
       </c>
       <c r="CM12" s="12">
@@ -3280,7 +3294,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="BY13" s="63">
+      <c r="BY13" s="58">
         <f t="shared" si="47"/>
         <v>0</v>
       </c>
@@ -3314,7 +3328,7 @@
         <f t="shared" ref="CK13" si="63">CJ13*$E13</f>
         <v>0</v>
       </c>
-      <c r="CL13" s="66"/>
+      <c r="CL13" s="61"/>
       <c r="CM13" s="12">
         <f t="shared" si="44"/>
         <v>0</v>
@@ -3518,7 +3532,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="BY14" s="63">
+      <c r="BY14" s="58">
         <f t="shared" si="47"/>
         <v>0</v>
       </c>
@@ -3552,7 +3566,7 @@
         <f t="shared" ref="CK14" si="67">CJ14*$E14</f>
         <v>0</v>
       </c>
-      <c r="CL14" s="66">
+      <c r="CL14" s="61">
         <v>106</v>
       </c>
       <c r="CM14" s="12">
@@ -3758,7 +3772,7 @@
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="BY15" s="63">
+      <c r="BY15" s="58">
         <f t="shared" si="47"/>
         <v>0</v>
       </c>
@@ -3792,104 +3806,104 @@
         <f t="shared" ref="CK15" si="71">CJ15*$E15</f>
         <v>0</v>
       </c>
-      <c r="CL15" s="66"/>
+      <c r="CL15" s="61"/>
       <c r="CM15" s="12">
         <f t="shared" si="44"/>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:91" s="62" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="50"/>
-      <c r="B16" s="50"/>
-      <c r="C16" s="57"/>
-      <c r="D16" s="50"/>
-      <c r="E16" s="58"/>
-      <c r="F16" s="55"/>
-      <c r="G16" s="59"/>
-      <c r="H16" s="52"/>
-      <c r="I16" s="51"/>
-      <c r="J16" s="52"/>
-      <c r="K16" s="51"/>
-      <c r="L16" s="52"/>
-      <c r="M16" s="51"/>
-      <c r="N16" s="52"/>
-      <c r="O16" s="51"/>
-      <c r="P16" s="52"/>
-      <c r="Q16" s="51"/>
-      <c r="R16" s="52"/>
-      <c r="S16" s="51"/>
-      <c r="T16" s="52"/>
-      <c r="U16" s="51"/>
-      <c r="V16" s="52"/>
-      <c r="W16" s="51"/>
-      <c r="X16" s="52"/>
-      <c r="Y16" s="51"/>
-      <c r="Z16" s="52"/>
-      <c r="AA16" s="51"/>
-      <c r="AB16" s="52"/>
-      <c r="AC16" s="51"/>
-      <c r="AD16" s="52"/>
-      <c r="AE16" s="51"/>
-      <c r="AF16" s="52"/>
-      <c r="AG16" s="51"/>
-      <c r="AH16" s="52"/>
-      <c r="AI16" s="51"/>
-      <c r="AJ16" s="52"/>
-      <c r="AK16" s="51"/>
-      <c r="AL16" s="52"/>
-      <c r="AM16" s="51"/>
-      <c r="AN16" s="52"/>
-      <c r="AO16" s="51"/>
-      <c r="AP16" s="52"/>
-      <c r="AQ16" s="51"/>
-      <c r="AR16" s="52"/>
-      <c r="AS16" s="51"/>
-      <c r="AT16" s="52"/>
-      <c r="AU16" s="51"/>
-      <c r="AV16" s="52"/>
-      <c r="AW16" s="51"/>
-      <c r="AX16" s="52"/>
-      <c r="AY16" s="51"/>
-      <c r="AZ16" s="52"/>
-      <c r="BA16" s="51"/>
-      <c r="BB16" s="52"/>
-      <c r="BC16" s="51"/>
-      <c r="BD16" s="52"/>
-      <c r="BE16" s="51"/>
-      <c r="BF16" s="52"/>
-      <c r="BG16" s="51"/>
-      <c r="BH16" s="52"/>
-      <c r="BI16" s="51"/>
-      <c r="BJ16" s="52"/>
-      <c r="BK16" s="51"/>
-      <c r="BL16" s="52"/>
-      <c r="BM16" s="51"/>
-      <c r="BN16" s="52"/>
-      <c r="BO16" s="51"/>
-      <c r="BP16" s="52"/>
-      <c r="BQ16" s="51"/>
-      <c r="BR16" s="52"/>
-      <c r="BS16" s="51"/>
-      <c r="BT16" s="60"/>
-      <c r="BU16" s="53"/>
-      <c r="BV16" s="51"/>
-      <c r="BW16" s="61"/>
-      <c r="BX16" s="51"/>
-      <c r="BY16" s="54"/>
-      <c r="BZ16" s="51"/>
-      <c r="CA16" s="56"/>
-      <c r="CB16" s="52"/>
-      <c r="CC16" s="52"/>
-      <c r="CD16" s="52"/>
-      <c r="CE16" s="52"/>
-      <c r="CF16" s="52"/>
-      <c r="CG16" s="52"/>
-      <c r="CH16" s="56"/>
-      <c r="CI16" s="52"/>
-      <c r="CJ16" s="52"/>
-      <c r="CK16" s="52"/>
-      <c r="CL16" s="55"/>
-      <c r="CM16" s="56"/>
+    <row r="16" spans="1:91" s="57" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="45"/>
+      <c r="B16" s="45"/>
+      <c r="C16" s="52"/>
+      <c r="D16" s="45"/>
+      <c r="E16" s="53"/>
+      <c r="F16" s="50"/>
+      <c r="G16" s="54"/>
+      <c r="H16" s="47"/>
+      <c r="I16" s="46"/>
+      <c r="J16" s="47"/>
+      <c r="K16" s="46"/>
+      <c r="L16" s="47"/>
+      <c r="M16" s="46"/>
+      <c r="N16" s="47"/>
+      <c r="O16" s="46"/>
+      <c r="P16" s="47"/>
+      <c r="Q16" s="46"/>
+      <c r="R16" s="47"/>
+      <c r="S16" s="46"/>
+      <c r="T16" s="47"/>
+      <c r="U16" s="46"/>
+      <c r="V16" s="47"/>
+      <c r="W16" s="46"/>
+      <c r="X16" s="47"/>
+      <c r="Y16" s="46"/>
+      <c r="Z16" s="47"/>
+      <c r="AA16" s="46"/>
+      <c r="AB16" s="47"/>
+      <c r="AC16" s="46"/>
+      <c r="AD16" s="47"/>
+      <c r="AE16" s="46"/>
+      <c r="AF16" s="47"/>
+      <c r="AG16" s="46"/>
+      <c r="AH16" s="47"/>
+      <c r="AI16" s="46"/>
+      <c r="AJ16" s="47"/>
+      <c r="AK16" s="46"/>
+      <c r="AL16" s="47"/>
+      <c r="AM16" s="46"/>
+      <c r="AN16" s="47"/>
+      <c r="AO16" s="46"/>
+      <c r="AP16" s="47"/>
+      <c r="AQ16" s="46"/>
+      <c r="AR16" s="47"/>
+      <c r="AS16" s="46"/>
+      <c r="AT16" s="47"/>
+      <c r="AU16" s="46"/>
+      <c r="AV16" s="47"/>
+      <c r="AW16" s="46"/>
+      <c r="AX16" s="47"/>
+      <c r="AY16" s="46"/>
+      <c r="AZ16" s="47"/>
+      <c r="BA16" s="46"/>
+      <c r="BB16" s="47"/>
+      <c r="BC16" s="46"/>
+      <c r="BD16" s="47"/>
+      <c r="BE16" s="46"/>
+      <c r="BF16" s="47"/>
+      <c r="BG16" s="46"/>
+      <c r="BH16" s="47"/>
+      <c r="BI16" s="46"/>
+      <c r="BJ16" s="47"/>
+      <c r="BK16" s="46"/>
+      <c r="BL16" s="47"/>
+      <c r="BM16" s="46"/>
+      <c r="BN16" s="47"/>
+      <c r="BO16" s="46"/>
+      <c r="BP16" s="47"/>
+      <c r="BQ16" s="46"/>
+      <c r="BR16" s="47"/>
+      <c r="BS16" s="46"/>
+      <c r="BT16" s="55"/>
+      <c r="BU16" s="48"/>
+      <c r="BV16" s="46"/>
+      <c r="BW16" s="56"/>
+      <c r="BX16" s="46"/>
+      <c r="BY16" s="49"/>
+      <c r="BZ16" s="46"/>
+      <c r="CA16" s="51"/>
+      <c r="CB16" s="47"/>
+      <c r="CC16" s="47"/>
+      <c r="CD16" s="47"/>
+      <c r="CE16" s="47"/>
+      <c r="CF16" s="47"/>
+      <c r="CG16" s="47"/>
+      <c r="CH16" s="51"/>
+      <c r="CI16" s="47"/>
+      <c r="CJ16" s="47"/>
+      <c r="CK16" s="47"/>
+      <c r="CL16" s="50"/>
+      <c r="CM16" s="51"/>
     </row>
     <row r="17" s="27" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="18" s="27" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -3911,7 +3925,7 @@
     <row r="34" s="27" customFormat="1" ht="15" x14ac:dyDescent="0.2"/>
   </sheetData>
   <sheetProtection insertRows="0"/>
-  <mergeCells count="50">
+  <mergeCells count="57">
     <mergeCell ref="F5:G6"/>
     <mergeCell ref="H5:BQ5"/>
     <mergeCell ref="AZ6:BA6"/>
@@ -3927,20 +3941,13 @@
     <mergeCell ref="AV6:AW6"/>
     <mergeCell ref="R6:S6"/>
     <mergeCell ref="T6:U6"/>
+    <mergeCell ref="V6:W6"/>
     <mergeCell ref="CH5:CI6"/>
     <mergeCell ref="CJ5:CK6"/>
     <mergeCell ref="CL5:CM6"/>
     <mergeCell ref="BW5:BX5"/>
     <mergeCell ref="AB6:AC6"/>
     <mergeCell ref="AX6:AY6"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="X6:Y6"/>
-    <mergeCell ref="Z6:AA6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="L6:M6"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="P6:Q6"/>
     <mergeCell ref="CF5:CG6"/>
     <mergeCell ref="CB6:CC6"/>
     <mergeCell ref="CD6:CE6"/>
@@ -3951,12 +3958,26 @@
     <mergeCell ref="BJ6:BK6"/>
     <mergeCell ref="BL6:BM6"/>
     <mergeCell ref="BN6:BO6"/>
+    <mergeCell ref="X6:Y6"/>
+    <mergeCell ref="Z6:AA6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="P6:Q6"/>
     <mergeCell ref="BP6:BQ6"/>
     <mergeCell ref="BY5:CA5"/>
     <mergeCell ref="CB5:CE5"/>
     <mergeCell ref="BR5:BS6"/>
-    <mergeCell ref="BT5:BT6"/>
     <mergeCell ref="BU5:BV5"/>
+    <mergeCell ref="BT5:BT7"/>
+    <mergeCell ref="BU6:BU7"/>
+    <mergeCell ref="BV6:BV7"/>
+    <mergeCell ref="BW6:BW7"/>
+    <mergeCell ref="BX6:BX7"/>
+    <mergeCell ref="BY6:BY7"/>
+    <mergeCell ref="BZ6:BZ7"/>
+    <mergeCell ref="CA6:CA7"/>
     <mergeCell ref="C5:C7"/>
     <mergeCell ref="D5:D7"/>
     <mergeCell ref="E5:E7"/>

--- a/test/data/excel/XNT_app_test.xlsx
+++ b/test/data/excel/XNT_app_test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nguyendn/Desktop/cim/import-export-backend/test/data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79CD0044-F69E-8F40-A17C-A3327EB0CFBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{169CB451-24C0-0A44-A8AA-4DF59025DB3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="600" yWindow="640" windowWidth="29640" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -702,6 +702,90 @@
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="2" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -743,90 +827,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1360,311 +1360,311 @@
       <c r="BQ4" s="28"/>
     </row>
     <row r="5" spans="1:91" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="71" t="s">
+      <c r="A5" s="99" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="74" t="s">
+      <c r="B5" s="102" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="62" t="s">
+      <c r="C5" s="90" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="65" t="s">
+      <c r="D5" s="93" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="68" t="s">
+      <c r="E5" s="96" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="93" t="s">
+      <c r="F5" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="G5" s="93"/>
-      <c r="H5" s="86" t="s">
+      <c r="G5" s="62"/>
+      <c r="H5" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="86"/>
-      <c r="J5" s="86"/>
-      <c r="K5" s="86"/>
-      <c r="L5" s="86"/>
-      <c r="M5" s="86"/>
-      <c r="N5" s="86"/>
-      <c r="O5" s="86"/>
-      <c r="P5" s="86"/>
-      <c r="Q5" s="86"/>
-      <c r="R5" s="86"/>
-      <c r="S5" s="86"/>
-      <c r="T5" s="86"/>
-      <c r="U5" s="86"/>
-      <c r="V5" s="86"/>
-      <c r="W5" s="86"/>
-      <c r="X5" s="86"/>
-      <c r="Y5" s="86"/>
-      <c r="Z5" s="86"/>
-      <c r="AA5" s="86"/>
-      <c r="AB5" s="86"/>
-      <c r="AC5" s="86"/>
-      <c r="AD5" s="86"/>
-      <c r="AE5" s="86"/>
-      <c r="AF5" s="86"/>
-      <c r="AG5" s="86"/>
-      <c r="AH5" s="86"/>
-      <c r="AI5" s="86"/>
-      <c r="AJ5" s="86"/>
-      <c r="AK5" s="86"/>
-      <c r="AL5" s="86"/>
-      <c r="AM5" s="86"/>
-      <c r="AN5" s="86"/>
-      <c r="AO5" s="86"/>
-      <c r="AP5" s="86"/>
-      <c r="AQ5" s="86"/>
-      <c r="AR5" s="86"/>
-      <c r="AS5" s="86"/>
-      <c r="AT5" s="86"/>
-      <c r="AU5" s="86"/>
-      <c r="AV5" s="86"/>
-      <c r="AW5" s="86"/>
-      <c r="AX5" s="86"/>
-      <c r="AY5" s="86"/>
-      <c r="AZ5" s="86"/>
-      <c r="BA5" s="86"/>
-      <c r="BB5" s="86"/>
-      <c r="BC5" s="86"/>
-      <c r="BD5" s="86"/>
-      <c r="BE5" s="86"/>
-      <c r="BF5" s="86"/>
-      <c r="BG5" s="86"/>
-      <c r="BH5" s="86"/>
-      <c r="BI5" s="86"/>
-      <c r="BJ5" s="86"/>
-      <c r="BK5" s="86"/>
-      <c r="BL5" s="86"/>
-      <c r="BM5" s="86"/>
-      <c r="BN5" s="86"/>
-      <c r="BO5" s="86"/>
-      <c r="BP5" s="86"/>
-      <c r="BQ5" s="86"/>
-      <c r="BR5" s="80" t="s">
+      <c r="I5" s="63"/>
+      <c r="J5" s="63"/>
+      <c r="K5" s="63"/>
+      <c r="L5" s="63"/>
+      <c r="M5" s="63"/>
+      <c r="N5" s="63"/>
+      <c r="O5" s="63"/>
+      <c r="P5" s="63"/>
+      <c r="Q5" s="63"/>
+      <c r="R5" s="63"/>
+      <c r="S5" s="63"/>
+      <c r="T5" s="63"/>
+      <c r="U5" s="63"/>
+      <c r="V5" s="63"/>
+      <c r="W5" s="63"/>
+      <c r="X5" s="63"/>
+      <c r="Y5" s="63"/>
+      <c r="Z5" s="63"/>
+      <c r="AA5" s="63"/>
+      <c r="AB5" s="63"/>
+      <c r="AC5" s="63"/>
+      <c r="AD5" s="63"/>
+      <c r="AE5" s="63"/>
+      <c r="AF5" s="63"/>
+      <c r="AG5" s="63"/>
+      <c r="AH5" s="63"/>
+      <c r="AI5" s="63"/>
+      <c r="AJ5" s="63"/>
+      <c r="AK5" s="63"/>
+      <c r="AL5" s="63"/>
+      <c r="AM5" s="63"/>
+      <c r="AN5" s="63"/>
+      <c r="AO5" s="63"/>
+      <c r="AP5" s="63"/>
+      <c r="AQ5" s="63"/>
+      <c r="AR5" s="63"/>
+      <c r="AS5" s="63"/>
+      <c r="AT5" s="63"/>
+      <c r="AU5" s="63"/>
+      <c r="AV5" s="63"/>
+      <c r="AW5" s="63"/>
+      <c r="AX5" s="63"/>
+      <c r="AY5" s="63"/>
+      <c r="AZ5" s="63"/>
+      <c r="BA5" s="63"/>
+      <c r="BB5" s="63"/>
+      <c r="BC5" s="63"/>
+      <c r="BD5" s="63"/>
+      <c r="BE5" s="63"/>
+      <c r="BF5" s="63"/>
+      <c r="BG5" s="63"/>
+      <c r="BH5" s="63"/>
+      <c r="BI5" s="63"/>
+      <c r="BJ5" s="63"/>
+      <c r="BK5" s="63"/>
+      <c r="BL5" s="63"/>
+      <c r="BM5" s="63"/>
+      <c r="BN5" s="63"/>
+      <c r="BO5" s="63"/>
+      <c r="BP5" s="63"/>
+      <c r="BQ5" s="63"/>
+      <c r="BR5" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="BS5" s="81"/>
-      <c r="BT5" s="84" t="s">
+      <c r="BS5" s="76"/>
+      <c r="BT5" s="79" t="s">
         <v>10</v>
       </c>
-      <c r="BU5" s="86" t="s">
+      <c r="BU5" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="BV5" s="86"/>
-      <c r="BW5" s="86" t="s">
+      <c r="BV5" s="63"/>
+      <c r="BW5" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="BX5" s="86"/>
-      <c r="BY5" s="76" t="s">
+      <c r="BX5" s="63"/>
+      <c r="BY5" s="71" t="s">
         <v>6</v>
       </c>
-      <c r="BZ5" s="76"/>
-      <c r="CA5" s="76"/>
-      <c r="CB5" s="77" t="s">
+      <c r="BZ5" s="71"/>
+      <c r="CA5" s="71"/>
+      <c r="CB5" s="72" t="s">
         <v>39</v>
       </c>
-      <c r="CC5" s="78"/>
-      <c r="CD5" s="78"/>
-      <c r="CE5" s="79"/>
-      <c r="CF5" s="87" t="s">
+      <c r="CC5" s="73"/>
+      <c r="CD5" s="73"/>
+      <c r="CE5" s="74"/>
+      <c r="CF5" s="65" t="s">
         <v>38</v>
       </c>
-      <c r="CG5" s="88"/>
-      <c r="CH5" s="87" t="s">
+      <c r="CG5" s="66"/>
+      <c r="CH5" s="65" t="s">
         <v>41</v>
       </c>
-      <c r="CI5" s="88"/>
-      <c r="CJ5" s="87" t="s">
+      <c r="CI5" s="66"/>
+      <c r="CJ5" s="65" t="s">
         <v>40</v>
       </c>
-      <c r="CK5" s="88"/>
-      <c r="CL5" s="91" t="s">
+      <c r="CK5" s="66"/>
+      <c r="CL5" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="CM5" s="91"/>
+      <c r="CM5" s="69"/>
     </row>
     <row r="6" spans="1:91" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="72"/>
-      <c r="B6" s="74"/>
-      <c r="C6" s="63"/>
-      <c r="D6" s="66"/>
-      <c r="E6" s="69"/>
-      <c r="F6" s="93"/>
-      <c r="G6" s="93"/>
-      <c r="H6" s="75">
+      <c r="A6" s="100"/>
+      <c r="B6" s="102"/>
+      <c r="C6" s="91"/>
+      <c r="D6" s="94"/>
+      <c r="E6" s="97"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="64">
         <v>1</v>
       </c>
-      <c r="I6" s="75"/>
-      <c r="J6" s="75">
+      <c r="I6" s="64"/>
+      <c r="J6" s="64">
         <v>2</v>
       </c>
-      <c r="K6" s="75"/>
-      <c r="L6" s="75">
+      <c r="K6" s="64"/>
+      <c r="L6" s="64">
         <v>3</v>
       </c>
-      <c r="M6" s="75"/>
-      <c r="N6" s="75">
+      <c r="M6" s="64"/>
+      <c r="N6" s="64">
         <v>4</v>
       </c>
-      <c r="O6" s="75"/>
-      <c r="P6" s="75">
+      <c r="O6" s="64"/>
+      <c r="P6" s="64">
         <v>5</v>
       </c>
-      <c r="Q6" s="75"/>
-      <c r="R6" s="75">
+      <c r="Q6" s="64"/>
+      <c r="R6" s="64">
         <v>6</v>
       </c>
-      <c r="S6" s="75"/>
-      <c r="T6" s="75">
+      <c r="S6" s="64"/>
+      <c r="T6" s="64">
         <v>7</v>
       </c>
-      <c r="U6" s="75"/>
-      <c r="V6" s="75">
+      <c r="U6" s="64"/>
+      <c r="V6" s="64">
         <v>8</v>
       </c>
-      <c r="W6" s="75"/>
-      <c r="X6" s="75">
+      <c r="W6" s="64"/>
+      <c r="X6" s="64">
         <v>9</v>
       </c>
-      <c r="Y6" s="75"/>
-      <c r="Z6" s="75">
+      <c r="Y6" s="64"/>
+      <c r="Z6" s="64">
         <v>10</v>
       </c>
-      <c r="AA6" s="75"/>
-      <c r="AB6" s="75">
-        <v>11</v>
-      </c>
-      <c r="AC6" s="75"/>
-      <c r="AD6" s="75">
+      <c r="AA6" s="64"/>
+      <c r="AB6" s="64">
+        <v>11</v>
+      </c>
+      <c r="AC6" s="64"/>
+      <c r="AD6" s="64">
         <v>12</v>
       </c>
-      <c r="AE6" s="75"/>
-      <c r="AF6" s="75">
+      <c r="AE6" s="64"/>
+      <c r="AF6" s="64">
         <v>13</v>
       </c>
-      <c r="AG6" s="75"/>
-      <c r="AH6" s="75">
+      <c r="AG6" s="64"/>
+      <c r="AH6" s="64">
         <v>14</v>
       </c>
-      <c r="AI6" s="75"/>
-      <c r="AJ6" s="75">
+      <c r="AI6" s="64"/>
+      <c r="AJ6" s="64">
         <v>15</v>
       </c>
-      <c r="AK6" s="75"/>
-      <c r="AL6" s="75">
+      <c r="AK6" s="64"/>
+      <c r="AL6" s="64">
         <v>16</v>
       </c>
-      <c r="AM6" s="75"/>
-      <c r="AN6" s="75">
+      <c r="AM6" s="64"/>
+      <c r="AN6" s="64">
         <v>17</v>
       </c>
-      <c r="AO6" s="75"/>
-      <c r="AP6" s="75">
+      <c r="AO6" s="64"/>
+      <c r="AP6" s="64">
         <v>18</v>
       </c>
-      <c r="AQ6" s="75"/>
-      <c r="AR6" s="75">
+      <c r="AQ6" s="64"/>
+      <c r="AR6" s="64">
         <v>19</v>
       </c>
-      <c r="AS6" s="75"/>
-      <c r="AT6" s="75">
+      <c r="AS6" s="64"/>
+      <c r="AT6" s="64">
         <v>20</v>
       </c>
-      <c r="AU6" s="75"/>
-      <c r="AV6" s="75">
+      <c r="AU6" s="64"/>
+      <c r="AV6" s="64">
         <v>21</v>
       </c>
-      <c r="AW6" s="75"/>
-      <c r="AX6" s="75">
+      <c r="AW6" s="64"/>
+      <c r="AX6" s="64">
         <v>22</v>
       </c>
-      <c r="AY6" s="75"/>
-      <c r="AZ6" s="75">
+      <c r="AY6" s="64"/>
+      <c r="AZ6" s="64">
         <v>23</v>
       </c>
-      <c r="BA6" s="75"/>
-      <c r="BB6" s="75">
+      <c r="BA6" s="64"/>
+      <c r="BB6" s="64">
         <v>24</v>
       </c>
-      <c r="BC6" s="75"/>
-      <c r="BD6" s="75">
+      <c r="BC6" s="64"/>
+      <c r="BD6" s="64">
         <v>25</v>
       </c>
-      <c r="BE6" s="75"/>
-      <c r="BF6" s="75">
+      <c r="BE6" s="64"/>
+      <c r="BF6" s="64">
         <v>26</v>
       </c>
-      <c r="BG6" s="75"/>
-      <c r="BH6" s="75">
+      <c r="BG6" s="64"/>
+      <c r="BH6" s="64">
         <v>27</v>
       </c>
-      <c r="BI6" s="75"/>
-      <c r="BJ6" s="75">
+      <c r="BI6" s="64"/>
+      <c r="BJ6" s="64">
         <v>28</v>
       </c>
-      <c r="BK6" s="75"/>
-      <c r="BL6" s="75">
+      <c r="BK6" s="64"/>
+      <c r="BL6" s="64">
         <v>29</v>
       </c>
-      <c r="BM6" s="75"/>
-      <c r="BN6" s="75">
+      <c r="BM6" s="64"/>
+      <c r="BN6" s="64">
         <v>30</v>
       </c>
-      <c r="BO6" s="75"/>
-      <c r="BP6" s="75">
+      <c r="BO6" s="64"/>
+      <c r="BP6" s="64">
         <v>31</v>
       </c>
-      <c r="BQ6" s="75"/>
-      <c r="BR6" s="82"/>
-      <c r="BS6" s="83"/>
-      <c r="BT6" s="94"/>
-      <c r="BU6" s="95" t="s">
-        <v>11</v>
-      </c>
-      <c r="BV6" s="97" t="s">
+      <c r="BQ6" s="64"/>
+      <c r="BR6" s="77"/>
+      <c r="BS6" s="78"/>
+      <c r="BT6" s="80"/>
+      <c r="BU6" s="82" t="s">
+        <v>11</v>
+      </c>
+      <c r="BV6" s="84" t="s">
         <v>13</v>
       </c>
-      <c r="BW6" s="99" t="s">
-        <v>11</v>
-      </c>
-      <c r="BX6" s="97" t="s">
+      <c r="BW6" s="86" t="s">
+        <v>11</v>
+      </c>
+      <c r="BX6" s="84" t="s">
         <v>13</v>
       </c>
-      <c r="BY6" s="101" t="s">
-        <v>11</v>
-      </c>
-      <c r="BZ6" s="97" t="s">
+      <c r="BY6" s="88" t="s">
+        <v>11</v>
+      </c>
+      <c r="BZ6" s="84" t="s">
         <v>12</v>
       </c>
-      <c r="CA6" s="97" t="s">
+      <c r="CA6" s="84" t="s">
         <v>13</v>
       </c>
-      <c r="CB6" s="92" t="s">
+      <c r="CB6" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="CC6" s="92"/>
-      <c r="CD6" s="92" t="s">
+      <c r="CC6" s="70"/>
+      <c r="CD6" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="CE6" s="92"/>
-      <c r="CF6" s="89"/>
-      <c r="CG6" s="90"/>
-      <c r="CH6" s="89"/>
-      <c r="CI6" s="90"/>
-      <c r="CJ6" s="89"/>
-      <c r="CK6" s="90"/>
-      <c r="CL6" s="91"/>
-      <c r="CM6" s="91"/>
+      <c r="CE6" s="70"/>
+      <c r="CF6" s="67"/>
+      <c r="CG6" s="68"/>
+      <c r="CH6" s="67"/>
+      <c r="CI6" s="68"/>
+      <c r="CJ6" s="67"/>
+      <c r="CK6" s="68"/>
+      <c r="CL6" s="69"/>
+      <c r="CM6" s="69"/>
     </row>
     <row r="7" spans="1:91" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="73"/>
-      <c r="B7" s="74"/>
-      <c r="C7" s="64"/>
-      <c r="D7" s="67"/>
-      <c r="E7" s="70"/>
+      <c r="A7" s="101"/>
+      <c r="B7" s="102"/>
+      <c r="C7" s="92"/>
+      <c r="D7" s="95"/>
+      <c r="E7" s="98"/>
       <c r="F7" s="59" t="s">
         <v>11</v>
       </c>
@@ -1863,14 +1863,14 @@
       <c r="BS7" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="BT7" s="85"/>
-      <c r="BU7" s="96"/>
-      <c r="BV7" s="98"/>
-      <c r="BW7" s="100"/>
-      <c r="BX7" s="98"/>
-      <c r="BY7" s="102"/>
-      <c r="BZ7" s="98"/>
-      <c r="CA7" s="98"/>
+      <c r="BT7" s="81"/>
+      <c r="BU7" s="83"/>
+      <c r="BV7" s="85"/>
+      <c r="BW7" s="87"/>
+      <c r="BX7" s="85"/>
+      <c r="BY7" s="89"/>
+      <c r="BZ7" s="85"/>
+      <c r="CA7" s="85"/>
       <c r="CB7" s="37" t="s">
         <v>11</v>
       </c>
@@ -3926,6 +3926,47 @@
   </sheetData>
   <sheetProtection insertRows="0"/>
   <mergeCells count="57">
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="D5:D7"/>
+    <mergeCell ref="E5:E7"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="BP6:BQ6"/>
+    <mergeCell ref="BY5:CA5"/>
+    <mergeCell ref="CB5:CE5"/>
+    <mergeCell ref="BR5:BS6"/>
+    <mergeCell ref="BU5:BV5"/>
+    <mergeCell ref="BT5:BT7"/>
+    <mergeCell ref="BU6:BU7"/>
+    <mergeCell ref="BV6:BV7"/>
+    <mergeCell ref="BW6:BW7"/>
+    <mergeCell ref="BX6:BX7"/>
+    <mergeCell ref="BY6:BY7"/>
+    <mergeCell ref="BZ6:BZ7"/>
+    <mergeCell ref="CA6:CA7"/>
+    <mergeCell ref="X6:Y6"/>
+    <mergeCell ref="Z6:AA6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="N6:O6"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="CH5:CI6"/>
+    <mergeCell ref="CJ5:CK6"/>
+    <mergeCell ref="CL5:CM6"/>
+    <mergeCell ref="BW5:BX5"/>
+    <mergeCell ref="AB6:AC6"/>
+    <mergeCell ref="AX6:AY6"/>
+    <mergeCell ref="CF5:CG6"/>
+    <mergeCell ref="CB6:CC6"/>
+    <mergeCell ref="CD6:CE6"/>
+    <mergeCell ref="BB6:BC6"/>
+    <mergeCell ref="BD6:BE6"/>
+    <mergeCell ref="BF6:BG6"/>
+    <mergeCell ref="BH6:BI6"/>
+    <mergeCell ref="BJ6:BK6"/>
+    <mergeCell ref="BL6:BM6"/>
+    <mergeCell ref="BN6:BO6"/>
     <mergeCell ref="F5:G6"/>
     <mergeCell ref="H5:BQ5"/>
     <mergeCell ref="AZ6:BA6"/>
@@ -3942,47 +3983,6 @@
     <mergeCell ref="R6:S6"/>
     <mergeCell ref="T6:U6"/>
     <mergeCell ref="V6:W6"/>
-    <mergeCell ref="CH5:CI6"/>
-    <mergeCell ref="CJ5:CK6"/>
-    <mergeCell ref="CL5:CM6"/>
-    <mergeCell ref="BW5:BX5"/>
-    <mergeCell ref="AB6:AC6"/>
-    <mergeCell ref="AX6:AY6"/>
-    <mergeCell ref="CF5:CG6"/>
-    <mergeCell ref="CB6:CC6"/>
-    <mergeCell ref="CD6:CE6"/>
-    <mergeCell ref="BB6:BC6"/>
-    <mergeCell ref="BD6:BE6"/>
-    <mergeCell ref="BF6:BG6"/>
-    <mergeCell ref="BH6:BI6"/>
-    <mergeCell ref="BJ6:BK6"/>
-    <mergeCell ref="BL6:BM6"/>
-    <mergeCell ref="BN6:BO6"/>
-    <mergeCell ref="X6:Y6"/>
-    <mergeCell ref="Z6:AA6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="L6:M6"/>
-    <mergeCell ref="N6:O6"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="BP6:BQ6"/>
-    <mergeCell ref="BY5:CA5"/>
-    <mergeCell ref="CB5:CE5"/>
-    <mergeCell ref="BR5:BS6"/>
-    <mergeCell ref="BU5:BV5"/>
-    <mergeCell ref="BT5:BT7"/>
-    <mergeCell ref="BU6:BU7"/>
-    <mergeCell ref="BV6:BV7"/>
-    <mergeCell ref="BW6:BW7"/>
-    <mergeCell ref="BX6:BX7"/>
-    <mergeCell ref="BY6:BY7"/>
-    <mergeCell ref="BZ6:BZ7"/>
-    <mergeCell ref="CA6:CA7"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="D5:D7"/>
-    <mergeCell ref="E5:E7"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="B5:B7"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
